--- a/data/trans_dic/IP16A08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia</t>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 24,66</t>
+          <t>2,9; 24,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 24,89</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,68</t>
+          <t>0,0; 25,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,44</t>
+          <t>0,0; 25,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,45</t>
+          <t>0,0; 40,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,63</t>
+          <t>0,0; 38,9</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 18,07</t>
+          <t>3,21; 17,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,49; 19,76</t>
+          <t>3,29; 19,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,35</t>
+          <t>0,0; 14,97</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,76</t>
+          <t>0,0; 17,1</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,38; 26,64</t>
+          <t>12,78; 27,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,52; 21,13</t>
+          <t>8,45; 21,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 22,53</t>
+          <t>9,71; 23,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 13,88</t>
+          <t>3,43; 15,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,91; 27,69</t>
+          <t>13,55; 26,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,68; 18,48</t>
+          <t>7,72; 18,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,33; 25,21</t>
+          <t>10,9; 24,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 17,55</t>
+          <t>6,66; 17,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,65; 24,47</t>
+          <t>14,75; 24,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 17,58</t>
+          <t>9,35; 17,06</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,94; 21,9</t>
+          <t>12,01; 21,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 14,43</t>
+          <t>5,95; 13,62</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 23,95</t>
+          <t>2,82; 24,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,58; 19,52</t>
+          <t>3,53; 19,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,92; 30,71</t>
+          <t>6,12; 31,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 22,21</t>
+          <t>4,3; 22,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,05; 25,55</t>
+          <t>5,8; 24,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,6; 26,96</t>
+          <t>7,09; 27,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 21,18</t>
+          <t>2,44; 20,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,1; 17,57</t>
+          <t>3,01; 17,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 19,26</t>
+          <t>4,95; 19,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,14; 19,89</t>
+          <t>7,45; 19,93</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 21,92</t>
+          <t>6,34; 21,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,99; 16,1</t>
+          <t>4,9; 16,28</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,94; 22,33</t>
+          <t>10,7; 21,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,09; 17,45</t>
+          <t>8,13; 17,22</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,42; 19,74</t>
+          <t>9,4; 19,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 12,78</t>
+          <t>4,38; 13,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,91; 22,08</t>
+          <t>11,97; 21,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,66; 17,5</t>
+          <t>8,43; 17,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 21,01</t>
+          <t>9,65; 20,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,57; 15,2</t>
+          <t>6,51; 15,07</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,82; 20,54</t>
+          <t>12,4; 19,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 16,14</t>
+          <t>9,35; 15,54</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,03; 19,7</t>
+          <t>10,78; 18,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,45; 12,44</t>
+          <t>6,3; 12,63</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2159</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3669</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>639; 5407</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5623</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5131</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4420</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3570</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6095</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1359; 7454</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1319; 7711</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3664</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5283</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>15313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12237</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13011</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17231</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12605</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>14752</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>13265</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>32544</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>24842</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>27763</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>23577</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>10318; 22282</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7459; 18576</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8057; 19438</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>4148; 18544</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>11877; 23646</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>7799; 18871</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9333; 21340</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>7999; 21391</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>24840; 41713</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>17694; 32286</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>20244; 36920</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>14337; 32814</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3363</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4613</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4674</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>4517</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>6080</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6563</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9443</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7344</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>8363</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>637; 5416</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1286; 7199</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1763; 8996</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1792; 9298</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2047; 8761</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>2796; 10851</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>705; 6033</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1400; 8042</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>2860; 11240</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>5650; 15118</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3657; 12588</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>4321; 14347</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>19366</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17758</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>17623</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14986</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>18609</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>42776</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>33595</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>13412; 26859</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>11969; 25357</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>11976; 25387</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>7776; 23123</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>17136; 31439</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>13322; 27433</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>11902; 25702</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>11853; 27454</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>33289; 52817</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>28536; 47421</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>27028; 45709</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>22666; 45449</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP16A08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Estudios-trans_dic.xlsx
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,9; 24,53</t>
+          <t>2,87; 24,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,9</t>
+          <t>2,53; 24,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,33</t>
+          <t>0,0; 28,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,26</t>
+          <t>0,0; 26,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,64</t>
+          <t>0,0; 36,45</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,9</t>
+          <t>0,0; 33,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 17,62</t>
+          <t>3,22; 19,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,29; 19,24</t>
+          <t>3,25; 18,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,97</t>
+          <t>0,0; 14,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,1</t>
+          <t>0,0; 18,77</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 27,61</t>
+          <t>12,58; 27,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,45; 21,05</t>
+          <t>8,62; 20,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,71; 23,43</t>
+          <t>9,69; 23,05</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 15,35</t>
+          <t>3,22; 14,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,55; 26,97</t>
+          <t>13,57; 27,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,72; 18,68</t>
+          <t>7,47; 19,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,9; 24,92</t>
+          <t>11,1; 24,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,66; 17,82</t>
+          <t>6,55; 17,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14,75; 24,77</t>
+          <t>15,28; 24,86</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,06</t>
+          <t>9,99; 17,92</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,01; 21,9</t>
+          <t>12,25; 21,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,95; 13,62</t>
+          <t>5,6; 14,03</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,82; 24,02</t>
+          <t>2,83; 24,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 19,77</t>
+          <t>3,5; 20,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,12; 31,24</t>
+          <t>6,17; 29,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,3; 22,33</t>
+          <t>4,21; 22,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,8; 24,84</t>
+          <t>5,41; 25,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,09; 27,52</t>
+          <t>7,19; 28,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,44; 20,9</t>
+          <t>2,41; 21,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 17,29</t>
+          <t>2,9; 17,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 19,44</t>
+          <t>6,06; 20,99</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,45; 19,93</t>
+          <t>7,08; 20,75</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,34; 21,83</t>
+          <t>6,52; 21,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,9; 16,28</t>
+          <t>5,29; 16,54</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,7; 21,43</t>
+          <t>10,34; 21,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,13; 17,22</t>
+          <t>8,3; 17,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,4; 19,92</t>
+          <t>9,27; 19,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,01</t>
+          <t>4,38; 12,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,97; 21,96</t>
+          <t>12,06; 21,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,43; 17,37</t>
+          <t>8,94; 18,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 20,85</t>
+          <t>9,82; 20,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 15,07</t>
+          <t>6,53; 15,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,4; 19,67</t>
+          <t>12,38; 20,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,35; 15,54</t>
+          <t>9,49; 15,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 18,23</t>
+          <t>10,9; 18,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 12,63</t>
+          <t>6,62; 12,52</t>
         </is>
       </c>
     </row>
@@ -1504,12 +1504,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>639; 5407</t>
+          <t>633; 5380</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5623</t>
+          <t>572; 5477</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1524,42 +1524,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5131</t>
+          <t>0; 5774</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4420</t>
+          <t>0; 4665</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3570</t>
+          <t>0; 3203</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6095</t>
+          <t>0; 5318</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1359; 7454</t>
+          <t>1363; 8206</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1319; 7711</t>
+          <t>1304; 7250</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3664</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5283</t>
+          <t>0; 5801</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10318; 22282</t>
+          <t>10153; 22143</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7459; 18576</t>
+          <t>7610; 18432</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8057; 19438</t>
+          <t>8043; 19129</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4148; 18544</t>
+          <t>3890; 17505</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11877; 23646</t>
+          <t>11896; 23748</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7799; 18871</t>
+          <t>7552; 19701</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9333; 21340</t>
+          <t>9505; 21312</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7999; 21391</t>
+          <t>7858; 21087</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24840; 41713</t>
+          <t>25736; 41858</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17694; 32286</t>
+          <t>18901; 33921</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20244; 36920</t>
+          <t>20660; 36045</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>14337; 32814</t>
+          <t>13483; 33797</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>637; 5416</t>
+          <t>639; 5425</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1286; 7199</t>
+          <t>1274; 7619</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1763; 8996</t>
+          <t>1777; 8493</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1792; 9298</t>
+          <t>1753; 9341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2047; 8761</t>
+          <t>1907; 8832</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2796; 10851</t>
+          <t>2834; 11354</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>705; 6033</t>
+          <t>696; 6293</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1400; 8042</t>
+          <t>1347; 8231</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2860; 11240</t>
+          <t>3505; 12136</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5650; 15118</t>
+          <t>5366; 15740</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3657; 12588</t>
+          <t>3762; 12294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4321; 14347</t>
+          <t>4663; 14581</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13412; 26859</t>
+          <t>12958; 26910</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11969; 25357</t>
+          <t>12225; 25543</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11976; 25387</t>
+          <t>11815; 24797</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7776; 23123</t>
+          <t>7779; 22522</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17136; 31439</t>
+          <t>17273; 31294</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13322; 27433</t>
+          <t>14124; 28594</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11902; 25702</t>
+          <t>12105; 25464</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11853; 27454</t>
+          <t>11891; 27497</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33289; 52817</t>
+          <t>33252; 53947</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28536; 47421</t>
+          <t>28961; 47480</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27028; 45709</t>
+          <t>27336; 45555</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22666; 45449</t>
+          <t>23828; 45074</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP16A08-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP16A08-Estudios-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,44 +649,44 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>8,21%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7,76%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,85%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>9,1%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>9,56%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10,56%</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
           <t>8,67%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 24,4</t>
+          <t>0,0; 25,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,53; 24,25</t>
+          <t>0,0; 23,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 42,45</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 36,23</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2,91; 24,66</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,48; 24,89</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 28,5</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 26,66</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 36,45</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 33,94</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 19,4</t>
+          <t>3,25; 18,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,25; 18,09</t>
+          <t>3,49; 19,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,35</t>
+          <t>0,0; 17,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,77</t>
+          <t>0,0; 23,04</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>19,65%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12,48%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,23%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>11,3%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>18,97%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15,68%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,65%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>12,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,58; 27,44</t>
+          <t>13,91; 27,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,62; 20,89</t>
+          <t>7,68; 18,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,69; 23,05</t>
+          <t>11,33; 25,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 14,49</t>
+          <t>6,53; 18,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,57; 27,09</t>
+          <t>12,38; 26,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 19,5</t>
+          <t>8,52; 21,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,1; 24,89</t>
+          <t>9,37; 22,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 17,57</t>
+          <t>6,71; 19,42</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>15,28; 24,86</t>
+          <t>14,65; 24,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,99; 17,92</t>
+          <t>9,55; 17,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,25; 21,38</t>
+          <t>11,94; 21,9</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,6; 14,03</t>
+          <t>8,01; 16,38</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,81%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,46%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,84%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,08%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>9,24%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>16,02%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,42%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 24,06</t>
+          <t>6,05; 25,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 20,93</t>
+          <t>7,6; 26,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,17; 29,5</t>
+          <t>2,41; 21,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 22,43</t>
+          <t>2,88; 17,47</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,41; 25,04</t>
+          <t>2,83; 23,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 28,79</t>
+          <t>3,58; 19,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 21,8</t>
+          <t>6,92; 30,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,9; 17,7</t>
+          <t>5,41; 24,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6,06; 20,99</t>
+          <t>5,41; 19,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,08; 20,75</t>
+          <t>7,14; 19,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 21,32</t>
+          <t>6,63; 21,92</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 16,54</t>
+          <t>5,12; 17,25</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16,35%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15,45%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>12,06%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>13,83%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>16,35%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,34; 21,48</t>
+          <t>11,91; 22,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,3; 17,35</t>
+          <t>8,66; 17,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9,27; 19,45</t>
+          <t>10,39; 21,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 12,67</t>
+          <t>6,71; 15,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,06; 21,85</t>
+          <t>10,94; 22,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,94; 18,1</t>
+          <t>8,09; 17,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 20,66</t>
+          <t>9,42; 19,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,53; 15,09</t>
+          <t>6,81; 16,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 20,09</t>
+          <t>12,82; 20,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,49; 15,56</t>
+          <t>9,27; 16,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 18,17</t>
+          <t>11,03; 19,7</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,52</t>
+          <t>7,77; 13,8</t>
         </is>
       </c>
     </row>
@@ -1246,13 +1246,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
+          <t>Menores que consumieron medicamentos para la alergia (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,62 +1436,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1663</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1359</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>2159</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1663</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1359</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3669</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3517</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>791</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>1655</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>3669</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>3517</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>1510</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>633; 5380</t>
+          <t>0; 5203</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>572; 5477</t>
+          <t>0; 4102</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 3729</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5043</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>641; 5437</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>560; 5619</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5774</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4665</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3203</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0; 5318</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1363; 8206</t>
+          <t>1374; 7645</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1304; 7250</t>
+          <t>1399; 7922</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 4248</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 5801</t>
+          <t>0; 5460</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17231</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12605</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14752</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12194</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>15313</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12237</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>13011</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>10312</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17231</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12605</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>14752</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13265</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23577</t>
+          <t>22769</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10153; 22143</t>
+          <t>12197; 24272</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7610; 18432</t>
+          <t>7764; 18669</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8043; 19129</t>
+          <t>9701; 21588</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3890; 17505</t>
+          <t>7049; 19419</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11896; 23748</t>
+          <t>9993; 21500</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7552; 19701</t>
+          <t>7515; 18647</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9505; 21312</t>
+          <t>7775; 18692</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7858; 21087</t>
+          <t>6221; 18001</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25736; 41858</t>
+          <t>24668; 41204</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18901; 33921</t>
+          <t>18079; 33276</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>20660; 36045</t>
+          <t>20135; 36915</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>13483; 33797</t>
+          <t>16063; 32849</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>4517</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>6080</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>3378</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>2047</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3363</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>4613</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>4674</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>4517</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6080</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2732</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8295</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>639; 5425</t>
+          <t>2134; 9010</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1274; 7619</t>
+          <t>2995; 10630</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1777; 8493</t>
+          <t>696; 6115</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1753; 9341</t>
+          <t>1242; 7534</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1907; 8832</t>
+          <t>639; 5401</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2834; 11354</t>
+          <t>1304; 7106</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>696; 6293</t>
+          <t>1994; 8843</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1347; 8231</t>
+          <t>2192; 9798</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3505; 12136</t>
+          <t>3125; 11133</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5366; 15740</t>
+          <t>5414; 15080</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3762; 12294</t>
+          <t>3821; 12638</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4663; 14581</t>
+          <t>4281; 14425</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23411</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>20044</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18275</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17083</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>19366</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>17758</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>17623</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>14986</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23411</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20044</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>18275</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>15492</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>33595</t>
+          <t>32574</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12958; 26910</t>
+          <t>17054; 31611</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12225; 25543</t>
+          <t>13676; 27640</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11815; 24797</t>
+          <t>12814; 25905</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7779; 22522</t>
+          <t>11064; 25466</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17273; 31294</t>
+          <t>13711; 27978</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14124; 28594</t>
+          <t>11906; 25693</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12105; 25464</t>
+          <t>12002; 25156</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11891; 27497</t>
+          <t>9733; 23447</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33252; 53947</t>
+          <t>34432; 55159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28961; 47480</t>
+          <t>28283; 49257</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>27336; 45555</t>
+          <t>27656; 49384</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>23828; 45074</t>
+          <t>23936; 42490</t>
         </is>
       </c>
     </row>
